--- a/Entregables/Itinerario-Garcia_Eduardo VNª0.5-Final.xlsx
+++ b/Entregables/Itinerario-Garcia_Eduardo VNª0.5-Final.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Universidad-7MO\Universidad-ESPE\Pasantias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{659CA0BF-8F68-4DCF-AAD5-A06618CA555B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D6F066C-571B-48CC-936E-70EF967FD4F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActividadesDetalle" sheetId="5" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -969,12 +969,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -987,29 +1002,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1017,8 +1017,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1325,15 +1325,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24.6" x14ac:dyDescent="0.6">
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A2" s="5" t="s">
@@ -1401,10 +1401,10 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="44">
+      <c r="A9" s="38">
         <v>46083</v>
       </c>
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="41" t="s">
         <v>199</v>
       </c>
       <c r="C9" s="14" t="s">
@@ -1414,17 +1414,17 @@
         <v>2</v>
       </c>
       <c r="E9" s="14"/>
-      <c r="F9" s="39" t="s">
+      <c r="F9" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="G9" s="42">
+      <c r="G9" s="47">
         <v>6</v>
       </c>
       <c r="H9" s="34"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A10" s="45"/>
-      <c r="B10" s="49"/>
+      <c r="A10" s="39"/>
+      <c r="B10" s="42"/>
       <c r="C10" s="14" t="s">
         <v>156</v>
       </c>
@@ -1434,13 +1434,13 @@
       <c r="E10" s="14">
         <v>6</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="47"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="48"/>
       <c r="H10" s="35"/>
     </row>
     <row r="11" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A11" s="46"/>
-      <c r="B11" s="50"/>
+      <c r="A11" s="40"/>
+      <c r="B11" s="43"/>
       <c r="C11" s="14" t="s">
         <v>17</v>
       </c>
@@ -1448,15 +1448,15 @@
         <v>2</v>
       </c>
       <c r="E11" s="14"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="43"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="49"/>
       <c r="H11" s="35"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A12" s="44">
+      <c r="A12" s="38">
         <v>46084</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="44" t="s">
         <v>22</v>
       </c>
       <c r="C12" s="14" t="s">
@@ -1475,8 +1475,8 @@
       <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A13" s="45"/>
-      <c r="B13" s="40"/>
+      <c r="A13" s="39"/>
+      <c r="B13" s="45"/>
       <c r="C13" s="14" t="s">
         <v>157</v>
       </c>
@@ -1489,8 +1489,8 @@
       <c r="H13" s="35"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A14" s="45"/>
-      <c r="B14" s="40"/>
+      <c r="A14" s="39"/>
+      <c r="B14" s="45"/>
       <c r="C14" s="14" t="s">
         <v>19</v>
       </c>
@@ -1505,8 +1505,8 @@
       <c r="H14" s="35"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A15" s="46"/>
-      <c r="B15" s="41"/>
+      <c r="A15" s="40"/>
+      <c r="B15" s="46"/>
       <c r="C15" s="14" t="s">
         <v>20</v>
       </c>
@@ -1519,10 +1519,10 @@
       <c r="H15" s="35"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A16" s="44">
+      <c r="A16" s="38">
         <v>46085</v>
       </c>
-      <c r="B16" s="48" t="s">
+      <c r="B16" s="41" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="14" t="s">
@@ -1541,8 +1541,8 @@
       <c r="H16" s="35"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A17" s="45"/>
-      <c r="B17" s="49"/>
+      <c r="A17" s="39"/>
+      <c r="B17" s="42"/>
       <c r="C17" s="14" t="s">
         <v>23</v>
       </c>
@@ -1557,8 +1557,8 @@
       <c r="H17" s="35"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A18" s="46"/>
-      <c r="B18" s="50"/>
+      <c r="A18" s="40"/>
+      <c r="B18" s="43"/>
       <c r="C18" s="14" t="s">
         <v>24</v>
       </c>
@@ -1571,10 +1571,10 @@
       <c r="H18" s="35"/>
     </row>
     <row r="19" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A19" s="44">
+      <c r="A19" s="38">
         <v>46086</v>
       </c>
-      <c r="B19" s="48" t="s">
+      <c r="B19" s="41" t="s">
         <v>198</v>
       </c>
       <c r="C19" s="14" t="s">
@@ -1593,8 +1593,8 @@
       <c r="H19" s="35"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A20" s="45"/>
-      <c r="B20" s="49"/>
+      <c r="A20" s="39"/>
+      <c r="B20" s="42"/>
       <c r="C20" s="14" t="s">
         <v>159</v>
       </c>
@@ -1609,8 +1609,8 @@
       <c r="H20" s="35"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A21" s="46"/>
-      <c r="B21" s="50"/>
+      <c r="A21" s="40"/>
+      <c r="B21" s="43"/>
       <c r="C21" s="14" t="s">
         <v>25</v>
       </c>
@@ -1623,10 +1623,10 @@
       <c r="H21" s="35"/>
     </row>
     <row r="22" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A22" s="44">
+      <c r="A22" s="38">
         <v>46087</v>
       </c>
-      <c r="B22" s="48" t="s">
+      <c r="B22" s="41" t="s">
         <v>160</v>
       </c>
       <c r="C22" s="14" t="s">
@@ -1636,17 +1636,17 @@
         <v>2</v>
       </c>
       <c r="E22" s="14"/>
-      <c r="F22" s="39" t="s">
+      <c r="F22" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="G22" s="42">
+      <c r="G22" s="47">
         <v>6</v>
       </c>
       <c r="H22" s="35"/>
     </row>
     <row r="23" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A23" s="45"/>
-      <c r="B23" s="49"/>
+      <c r="A23" s="39"/>
+      <c r="B23" s="42"/>
       <c r="C23" s="14" t="s">
         <v>162</v>
       </c>
@@ -1656,13 +1656,13 @@
       <c r="E23" s="14">
         <v>6</v>
       </c>
-      <c r="F23" s="40"/>
-      <c r="G23" s="47"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="48"/>
       <c r="H23" s="35"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A24" s="45"/>
-      <c r="B24" s="49"/>
+      <c r="A24" s="39"/>
+      <c r="B24" s="42"/>
       <c r="C24" s="14" t="s">
         <v>26</v>
       </c>
@@ -1670,13 +1670,13 @@
         <v>1</v>
       </c>
       <c r="E24" s="14"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="47"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="48"/>
       <c r="H24" s="35"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A25" s="46"/>
-      <c r="B25" s="50"/>
+      <c r="A25" s="40"/>
+      <c r="B25" s="43"/>
       <c r="C25" s="14" t="s">
         <v>27</v>
       </c>
@@ -1684,15 +1684,15 @@
         <v>2</v>
       </c>
       <c r="E25" s="14"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="43"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="49"/>
       <c r="H25" s="35"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A26" s="44">
+      <c r="A26" s="38">
         <v>46090</v>
       </c>
-      <c r="B26" s="48" t="s">
+      <c r="B26" s="41" t="s">
         <v>163</v>
       </c>
       <c r="C26" s="16" t="s">
@@ -1702,17 +1702,17 @@
         <v>1</v>
       </c>
       <c r="E26" s="14"/>
-      <c r="F26" s="39" t="s">
+      <c r="F26" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G26" s="42">
+      <c r="G26" s="47">
         <v>6</v>
       </c>
       <c r="H26" s="35"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A27" s="45"/>
-      <c r="B27" s="49"/>
+      <c r="A27" s="39"/>
+      <c r="B27" s="42"/>
       <c r="C27" s="14" t="s">
         <v>28</v>
       </c>
@@ -1722,13 +1722,13 @@
       <c r="E27" s="14">
         <v>6</v>
       </c>
-      <c r="F27" s="40"/>
-      <c r="G27" s="47"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="48"/>
       <c r="H27" s="35"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A28" s="45"/>
-      <c r="B28" s="49"/>
+      <c r="A28" s="39"/>
+      <c r="B28" s="42"/>
       <c r="C28" s="14" t="s">
         <v>165</v>
       </c>
@@ -1736,13 +1736,13 @@
         <v>2</v>
       </c>
       <c r="E28" s="14"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="47"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="48"/>
       <c r="H28" s="35"/>
     </row>
     <row r="29" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A29" s="46"/>
-      <c r="B29" s="50"/>
+      <c r="A29" s="40"/>
+      <c r="B29" s="43"/>
       <c r="C29" s="14" t="s">
         <v>166</v>
       </c>
@@ -1750,15 +1750,15 @@
         <v>2</v>
       </c>
       <c r="E29" s="14"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="43"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="49"/>
       <c r="H29" s="35"/>
     </row>
     <row r="30" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A30" s="44">
+      <c r="A30" s="38">
         <v>46091</v>
       </c>
-      <c r="B30" s="48" t="s">
+      <c r="B30" s="41" t="s">
         <v>167</v>
       </c>
       <c r="C30" s="14" t="s">
@@ -1768,17 +1768,17 @@
         <v>2</v>
       </c>
       <c r="E30" s="14"/>
-      <c r="F30" s="39" t="s">
+      <c r="F30" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G30" s="42">
+      <c r="G30" s="47">
         <v>6</v>
       </c>
       <c r="H30" s="35"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A31" s="45"/>
-      <c r="B31" s="49"/>
+      <c r="A31" s="39"/>
+      <c r="B31" s="42"/>
       <c r="C31" s="14" t="s">
         <v>169</v>
       </c>
@@ -1788,13 +1788,13 @@
       <c r="E31" s="14">
         <v>6</v>
       </c>
-      <c r="F31" s="40"/>
-      <c r="G31" s="47"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="48"/>
       <c r="H31" s="35"/>
     </row>
     <row r="32" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A32" s="46"/>
-      <c r="B32" s="50"/>
+      <c r="A32" s="40"/>
+      <c r="B32" s="43"/>
       <c r="C32" s="14" t="s">
         <v>170</v>
       </c>
@@ -1802,15 +1802,15 @@
         <v>2</v>
       </c>
       <c r="E32" s="14"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="43"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="49"/>
       <c r="H32" s="35"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A33" s="44">
+      <c r="A33" s="38">
         <v>46092</v>
       </c>
-      <c r="B33" s="48" t="s">
+      <c r="B33" s="41" t="s">
         <v>31</v>
       </c>
       <c r="C33" s="17" t="s">
@@ -1820,17 +1820,17 @@
         <v>1</v>
       </c>
       <c r="E33" s="14"/>
-      <c r="F33" s="39" t="s">
+      <c r="F33" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G33" s="42">
+      <c r="G33" s="47">
         <v>6</v>
       </c>
       <c r="H33" s="35"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A34" s="45"/>
-      <c r="B34" s="49"/>
+      <c r="A34" s="39"/>
+      <c r="B34" s="42"/>
       <c r="C34" s="14" t="s">
         <v>33</v>
       </c>
@@ -1840,13 +1840,13 @@
       <c r="E34" s="14">
         <v>6</v>
       </c>
-      <c r="F34" s="40"/>
-      <c r="G34" s="47"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="48"/>
       <c r="H34" s="35"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A35" s="45"/>
-      <c r="B35" s="49"/>
+      <c r="A35" s="39"/>
+      <c r="B35" s="42"/>
       <c r="C35" s="14" t="s">
         <v>34</v>
       </c>
@@ -1854,13 +1854,13 @@
         <v>2</v>
       </c>
       <c r="E35" s="14"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="47"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="48"/>
       <c r="H35" s="35"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A36" s="46"/>
-      <c r="B36" s="50"/>
+      <c r="A36" s="40"/>
+      <c r="B36" s="43"/>
       <c r="C36" s="14" t="s">
         <v>35</v>
       </c>
@@ -1868,15 +1868,15 @@
         <v>2</v>
       </c>
       <c r="E36" s="14"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="43"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="49"/>
       <c r="H36" s="35"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A37" s="44">
+      <c r="A37" s="38">
         <v>46093</v>
       </c>
-      <c r="B37" s="48" t="s">
+      <c r="B37" s="41" t="s">
         <v>36</v>
       </c>
       <c r="C37" s="14" t="s">
@@ -1886,17 +1886,17 @@
         <v>2</v>
       </c>
       <c r="E37" s="14"/>
-      <c r="F37" s="39" t="s">
+      <c r="F37" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G37" s="42">
+      <c r="G37" s="47">
         <v>6</v>
       </c>
       <c r="H37" s="35"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A38" s="45"/>
-      <c r="B38" s="49"/>
+      <c r="A38" s="39"/>
+      <c r="B38" s="42"/>
       <c r="C38" s="14" t="s">
         <v>38</v>
       </c>
@@ -1906,13 +1906,13 @@
       <c r="E38" s="14">
         <v>6</v>
       </c>
-      <c r="F38" s="40"/>
-      <c r="G38" s="47"/>
+      <c r="F38" s="45"/>
+      <c r="G38" s="48"/>
       <c r="H38" s="35"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A39" s="45"/>
-      <c r="B39" s="49"/>
+      <c r="A39" s="39"/>
+      <c r="B39" s="42"/>
       <c r="C39" s="14" t="s">
         <v>39</v>
       </c>
@@ -1920,13 +1920,13 @@
         <v>2</v>
       </c>
       <c r="E39" s="14"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="47"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="48"/>
       <c r="H39" s="35"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A40" s="46"/>
-      <c r="B40" s="50"/>
+      <c r="A40" s="40"/>
+      <c r="B40" s="43"/>
       <c r="C40" s="14" t="s">
         <v>40</v>
       </c>
@@ -1934,15 +1934,15 @@
         <v>2</v>
       </c>
       <c r="E40" s="14"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="43"/>
+      <c r="F40" s="46"/>
+      <c r="G40" s="49"/>
       <c r="H40" s="35"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A41" s="44">
+      <c r="A41" s="38">
         <v>46094</v>
       </c>
-      <c r="B41" s="39" t="s">
+      <c r="B41" s="44" t="s">
         <v>41</v>
       </c>
       <c r="C41" s="17" t="s">
@@ -1961,8 +1961,8 @@
       <c r="H41" s="35"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A42" s="45"/>
-      <c r="B42" s="40"/>
+      <c r="A42" s="39"/>
+      <c r="B42" s="45"/>
       <c r="C42" s="14" t="s">
         <v>43</v>
       </c>
@@ -1977,8 +1977,8 @@
       <c r="H42" s="35"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A43" s="45"/>
-      <c r="B43" s="40"/>
+      <c r="A43" s="39"/>
+      <c r="B43" s="45"/>
       <c r="C43" s="14" t="s">
         <v>44</v>
       </c>
@@ -1991,8 +1991,8 @@
       <c r="H43" s="35"/>
     </row>
     <row r="44" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A44" s="46"/>
-      <c r="B44" s="41"/>
+      <c r="A44" s="40"/>
+      <c r="B44" s="46"/>
       <c r="C44" s="14" t="s">
         <v>45</v>
       </c>
@@ -2005,10 +2005,10 @@
       <c r="H44" s="35"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A45" s="44">
+      <c r="A45" s="38">
         <v>46097</v>
       </c>
-      <c r="B45" s="48" t="s">
+      <c r="B45" s="41" t="s">
         <v>171</v>
       </c>
       <c r="C45" s="26" t="s">
@@ -2018,17 +2018,17 @@
         <v>2</v>
       </c>
       <c r="E45" s="14"/>
-      <c r="F45" s="39" t="s">
+      <c r="F45" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G45" s="42">
+      <c r="G45" s="47">
         <v>6</v>
       </c>
       <c r="H45" s="35"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A46" s="45"/>
-      <c r="B46" s="49"/>
+      <c r="A46" s="39"/>
+      <c r="B46" s="42"/>
       <c r="C46" s="26" t="s">
         <v>47</v>
       </c>
@@ -2038,13 +2038,13 @@
       <c r="E46" s="14">
         <v>6</v>
       </c>
-      <c r="F46" s="40"/>
-      <c r="G46" s="47"/>
+      <c r="F46" s="45"/>
+      <c r="G46" s="48"/>
       <c r="H46" s="35"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A47" s="46"/>
-      <c r="B47" s="50"/>
+      <c r="A47" s="40"/>
+      <c r="B47" s="43"/>
       <c r="C47" s="26" t="s">
         <v>48</v>
       </c>
@@ -2052,15 +2052,15 @@
         <v>2</v>
       </c>
       <c r="E47" s="14"/>
-      <c r="F47" s="41"/>
-      <c r="G47" s="43"/>
+      <c r="F47" s="46"/>
+      <c r="G47" s="49"/>
       <c r="H47" s="35"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A48" s="44">
+      <c r="A48" s="38">
         <v>46098</v>
       </c>
-      <c r="B48" s="48" t="s">
+      <c r="B48" s="41" t="s">
         <v>172</v>
       </c>
       <c r="C48" s="26" t="s">
@@ -2070,17 +2070,17 @@
         <v>2</v>
       </c>
       <c r="E48" s="14"/>
-      <c r="F48" s="39" t="s">
+      <c r="F48" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G48" s="42">
+      <c r="G48" s="47">
         <v>6</v>
       </c>
       <c r="H48" s="35"/>
     </row>
     <row r="49" spans="1:10" ht="36" x14ac:dyDescent="0.5">
-      <c r="A49" s="45"/>
-      <c r="B49" s="49"/>
+      <c r="A49" s="39"/>
+      <c r="B49" s="42"/>
       <c r="C49" s="26" t="s">
         <v>49</v>
       </c>
@@ -2090,13 +2090,13 @@
       <c r="E49" s="14">
         <v>6</v>
       </c>
-      <c r="F49" s="40"/>
-      <c r="G49" s="47"/>
+      <c r="F49" s="45"/>
+      <c r="G49" s="48"/>
       <c r="H49" s="35"/>
     </row>
     <row r="50" spans="1:10" ht="36" x14ac:dyDescent="0.5">
-      <c r="A50" s="46"/>
-      <c r="B50" s="50"/>
+      <c r="A50" s="40"/>
+      <c r="B50" s="43"/>
       <c r="C50" s="26" t="s">
         <v>50</v>
       </c>
@@ -2104,16 +2104,16 @@
         <v>2</v>
       </c>
       <c r="E50" s="14"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="43"/>
+      <c r="F50" s="46"/>
+      <c r="G50" s="49"/>
       <c r="H50" s="35"/>
       <c r="J50" s="10"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A51" s="44">
+      <c r="A51" s="38">
         <v>46099</v>
       </c>
-      <c r="B51" s="48" t="s">
+      <c r="B51" s="41" t="s">
         <v>51</v>
       </c>
       <c r="C51" s="26" t="s">
@@ -2123,17 +2123,17 @@
         <v>1</v>
       </c>
       <c r="E51" s="14"/>
-      <c r="F51" s="39" t="s">
+      <c r="F51" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G51" s="42">
+      <c r="G51" s="47">
         <v>6</v>
       </c>
       <c r="H51" s="35"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A52" s="45"/>
-      <c r="B52" s="49"/>
+      <c r="A52" s="39"/>
+      <c r="B52" s="42"/>
       <c r="C52" s="26" t="s">
         <v>53</v>
       </c>
@@ -2143,13 +2143,13 @@
       <c r="E52" s="14">
         <v>6</v>
       </c>
-      <c r="F52" s="40"/>
-      <c r="G52" s="47"/>
+      <c r="F52" s="45"/>
+      <c r="G52" s="48"/>
       <c r="H52" s="35"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A53" s="46"/>
-      <c r="B53" s="50"/>
+      <c r="A53" s="40"/>
+      <c r="B53" s="43"/>
       <c r="C53" s="26" t="s">
         <v>54</v>
       </c>
@@ -2157,16 +2157,16 @@
         <v>3</v>
       </c>
       <c r="E53" s="14"/>
-      <c r="F53" s="41"/>
-      <c r="G53" s="43"/>
+      <c r="F53" s="46"/>
+      <c r="G53" s="49"/>
       <c r="H53" s="35"/>
       <c r="J53" s="10"/>
     </row>
     <row r="54" spans="1:10" ht="36" x14ac:dyDescent="0.5">
-      <c r="A54" s="44">
+      <c r="A54" s="38">
         <v>46100</v>
       </c>
-      <c r="B54" s="48" t="s">
+      <c r="B54" s="41" t="s">
         <v>55</v>
       </c>
       <c r="C54" s="26" t="s">
@@ -2176,17 +2176,17 @@
         <v>2</v>
       </c>
       <c r="E54" s="14"/>
-      <c r="F54" s="39" t="s">
+      <c r="F54" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G54" s="42">
+      <c r="G54" s="47">
         <v>6</v>
       </c>
       <c r="H54" s="35"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A55" s="45"/>
-      <c r="B55" s="49"/>
+      <c r="A55" s="39"/>
+      <c r="B55" s="42"/>
       <c r="C55" s="26" t="s">
         <v>57</v>
       </c>
@@ -2196,13 +2196,13 @@
       <c r="E55" s="14">
         <v>6</v>
       </c>
-      <c r="F55" s="40"/>
-      <c r="G55" s="47"/>
+      <c r="F55" s="45"/>
+      <c r="G55" s="48"/>
       <c r="H55" s="35"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A56" s="46"/>
-      <c r="B56" s="50"/>
+      <c r="A56" s="40"/>
+      <c r="B56" s="43"/>
       <c r="C56" s="26" t="s">
         <v>58</v>
       </c>
@@ -2210,15 +2210,15 @@
         <v>2</v>
       </c>
       <c r="E56" s="14"/>
-      <c r="F56" s="41"/>
-      <c r="G56" s="43"/>
+      <c r="F56" s="46"/>
+      <c r="G56" s="49"/>
       <c r="H56" s="35"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A57" s="44">
+      <c r="A57" s="38">
         <v>46101</v>
       </c>
-      <c r="B57" s="48" t="s">
+      <c r="B57" s="41" t="s">
         <v>59</v>
       </c>
       <c r="C57" s="26" t="s">
@@ -2228,17 +2228,17 @@
         <v>2</v>
       </c>
       <c r="E57" s="14"/>
-      <c r="F57" s="39" t="s">
+      <c r="F57" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G57" s="42">
+      <c r="G57" s="47">
         <v>6</v>
       </c>
       <c r="H57" s="35"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A58" s="45"/>
-      <c r="B58" s="49"/>
+      <c r="A58" s="39"/>
+      <c r="B58" s="42"/>
       <c r="C58" s="26" t="s">
         <v>61</v>
       </c>
@@ -2248,13 +2248,13 @@
       <c r="E58" s="14">
         <v>6</v>
       </c>
-      <c r="F58" s="40"/>
-      <c r="G58" s="47"/>
+      <c r="F58" s="45"/>
+      <c r="G58" s="48"/>
       <c r="H58" s="35"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A59" s="46"/>
-      <c r="B59" s="50"/>
+      <c r="A59" s="40"/>
+      <c r="B59" s="43"/>
       <c r="C59" s="26" t="s">
         <v>62</v>
       </c>
@@ -2262,15 +2262,15 @@
         <v>2</v>
       </c>
       <c r="E59" s="14"/>
-      <c r="F59" s="41"/>
-      <c r="G59" s="43"/>
+      <c r="F59" s="46"/>
+      <c r="G59" s="49"/>
       <c r="H59" s="35"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A60" s="44">
+      <c r="A60" s="38">
         <v>46104</v>
       </c>
-      <c r="B60" s="48" t="s">
+      <c r="B60" s="41" t="s">
         <v>68</v>
       </c>
       <c r="C60" s="26" t="s">
@@ -2280,17 +2280,17 @@
         <v>1</v>
       </c>
       <c r="E60" s="14"/>
-      <c r="F60" s="39" t="s">
+      <c r="F60" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G60" s="42">
+      <c r="G60" s="47">
         <v>6</v>
       </c>
       <c r="H60" s="35"/>
     </row>
     <row r="61" spans="1:10" ht="36" x14ac:dyDescent="0.5">
-      <c r="A61" s="45"/>
-      <c r="B61" s="49"/>
+      <c r="A61" s="39"/>
+      <c r="B61" s="42"/>
       <c r="C61" s="26" t="s">
         <v>64</v>
       </c>
@@ -2300,13 +2300,13 @@
       <c r="E61" s="14">
         <v>6</v>
       </c>
-      <c r="F61" s="40"/>
-      <c r="G61" s="47"/>
+      <c r="F61" s="45"/>
+      <c r="G61" s="48"/>
       <c r="H61" s="35"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A62" s="45"/>
-      <c r="B62" s="49"/>
+      <c r="A62" s="39"/>
+      <c r="B62" s="42"/>
       <c r="C62" s="26" t="s">
         <v>65</v>
       </c>
@@ -2314,13 +2314,13 @@
         <v>2</v>
       </c>
       <c r="E62" s="14"/>
-      <c r="F62" s="40"/>
-      <c r="G62" s="47"/>
+      <c r="F62" s="45"/>
+      <c r="G62" s="48"/>
       <c r="H62" s="35"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A63" s="46"/>
-      <c r="B63" s="50"/>
+      <c r="A63" s="40"/>
+      <c r="B63" s="43"/>
       <c r="C63" s="26" t="s">
         <v>66</v>
       </c>
@@ -2328,16 +2328,16 @@
         <v>1</v>
       </c>
       <c r="E63" s="14"/>
-      <c r="F63" s="41"/>
-      <c r="G63" s="43"/>
+      <c r="F63" s="46"/>
+      <c r="G63" s="49"/>
       <c r="H63" s="35"/>
       <c r="J63" s="10"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A64" s="44">
+      <c r="A64" s="38">
         <v>46105</v>
       </c>
-      <c r="B64" s="48" t="s">
+      <c r="B64" s="41" t="s">
         <v>67</v>
       </c>
       <c r="C64" s="26" t="s">
@@ -2347,17 +2347,17 @@
         <v>1</v>
       </c>
       <c r="E64" s="13"/>
-      <c r="F64" s="39" t="s">
+      <c r="F64" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G64" s="42">
+      <c r="G64" s="47">
         <v>6</v>
       </c>
       <c r="H64" s="35"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A65" s="45"/>
-      <c r="B65" s="49"/>
+      <c r="A65" s="39"/>
+      <c r="B65" s="42"/>
       <c r="C65" s="26" t="s">
         <v>70</v>
       </c>
@@ -2365,13 +2365,13 @@
         <v>2</v>
       </c>
       <c r="E65" s="13"/>
-      <c r="F65" s="40"/>
-      <c r="G65" s="47"/>
+      <c r="F65" s="45"/>
+      <c r="G65" s="48"/>
       <c r="H65" s="35"/>
     </row>
     <row r="66" spans="1:10" ht="36" x14ac:dyDescent="0.5">
-      <c r="A66" s="45"/>
-      <c r="B66" s="49"/>
+      <c r="A66" s="39"/>
+      <c r="B66" s="42"/>
       <c r="C66" s="26" t="s">
         <v>71</v>
       </c>
@@ -2381,13 +2381,13 @@
       <c r="E66" s="29">
         <v>6</v>
       </c>
-      <c r="F66" s="40"/>
-      <c r="G66" s="47"/>
+      <c r="F66" s="45"/>
+      <c r="G66" s="48"/>
       <c r="H66" s="35"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A67" s="46"/>
-      <c r="B67" s="50"/>
+      <c r="A67" s="40"/>
+      <c r="B67" s="43"/>
       <c r="C67" s="26" t="s">
         <v>72</v>
       </c>
@@ -2395,16 +2395,16 @@
         <v>1</v>
       </c>
       <c r="E67" s="14"/>
-      <c r="F67" s="41"/>
-      <c r="G67" s="43"/>
+      <c r="F67" s="46"/>
+      <c r="G67" s="49"/>
       <c r="H67" s="35"/>
       <c r="J67" s="10"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A68" s="44">
+      <c r="A68" s="38">
         <v>46106</v>
       </c>
-      <c r="B68" s="48" t="s">
+      <c r="B68" s="41" t="s">
         <v>73</v>
       </c>
       <c r="C68" s="26" t="s">
@@ -2414,17 +2414,17 @@
         <v>1</v>
       </c>
       <c r="E68" s="13"/>
-      <c r="F68" s="39" t="s">
+      <c r="F68" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G68" s="42">
+      <c r="G68" s="47">
         <v>6</v>
       </c>
       <c r="H68" s="35"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A69" s="45"/>
-      <c r="B69" s="49"/>
+      <c r="A69" s="39"/>
+      <c r="B69" s="42"/>
       <c r="C69" s="26" t="s">
         <v>75</v>
       </c>
@@ -2432,13 +2432,13 @@
         <v>1</v>
       </c>
       <c r="E69" s="13"/>
-      <c r="F69" s="40"/>
-      <c r="G69" s="47"/>
+      <c r="F69" s="45"/>
+      <c r="G69" s="48"/>
       <c r="H69" s="35"/>
     </row>
     <row r="70" spans="1:10" ht="36" x14ac:dyDescent="0.5">
-      <c r="A70" s="45"/>
-      <c r="B70" s="49"/>
+      <c r="A70" s="39"/>
+      <c r="B70" s="42"/>
       <c r="C70" s="26" t="s">
         <v>76</v>
       </c>
@@ -2448,13 +2448,13 @@
       <c r="E70" s="29">
         <v>6</v>
       </c>
-      <c r="F70" s="40"/>
-      <c r="G70" s="47"/>
+      <c r="F70" s="45"/>
+      <c r="G70" s="48"/>
       <c r="H70" s="35"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A71" s="46"/>
-      <c r="B71" s="50"/>
+      <c r="A71" s="40"/>
+      <c r="B71" s="43"/>
       <c r="C71" s="26" t="s">
         <v>77</v>
       </c>
@@ -2462,15 +2462,15 @@
         <v>2</v>
       </c>
       <c r="E71" s="14"/>
-      <c r="F71" s="41"/>
-      <c r="G71" s="43"/>
+      <c r="F71" s="46"/>
+      <c r="G71" s="49"/>
       <c r="H71" s="35"/>
     </row>
     <row r="72" spans="1:10" ht="36" x14ac:dyDescent="0.5">
-      <c r="A72" s="44">
+      <c r="A72" s="38">
         <v>46107</v>
       </c>
-      <c r="B72" s="48" t="s">
+      <c r="B72" s="41" t="s">
         <v>78</v>
       </c>
       <c r="C72" s="26" t="s">
@@ -2480,17 +2480,17 @@
         <v>2</v>
       </c>
       <c r="E72" s="13"/>
-      <c r="F72" s="39" t="s">
+      <c r="F72" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G72" s="42">
+      <c r="G72" s="47">
         <v>6</v>
       </c>
       <c r="H72" s="35"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A73" s="45"/>
-      <c r="B73" s="49"/>
+      <c r="A73" s="39"/>
+      <c r="B73" s="42"/>
       <c r="C73" s="26" t="s">
         <v>80</v>
       </c>
@@ -2500,13 +2500,13 @@
       <c r="E73" s="29">
         <v>6</v>
       </c>
-      <c r="F73" s="40"/>
-      <c r="G73" s="47"/>
+      <c r="F73" s="45"/>
+      <c r="G73" s="48"/>
       <c r="H73" s="35"/>
     </row>
     <row r="74" spans="1:10" ht="36" x14ac:dyDescent="0.5">
-      <c r="A74" s="46"/>
-      <c r="B74" s="50"/>
+      <c r="A74" s="40"/>
+      <c r="B74" s="43"/>
       <c r="C74" s="26" t="s">
         <v>81</v>
       </c>
@@ -2514,15 +2514,15 @@
         <v>2</v>
       </c>
       <c r="E74" s="14"/>
-      <c r="F74" s="41"/>
-      <c r="G74" s="43"/>
+      <c r="F74" s="46"/>
+      <c r="G74" s="49"/>
       <c r="H74" s="35"/>
     </row>
     <row r="75" spans="1:10" ht="36" x14ac:dyDescent="0.5">
-      <c r="A75" s="44">
+      <c r="A75" s="38">
         <v>46108</v>
       </c>
-      <c r="B75" s="48" t="s">
+      <c r="B75" s="41" t="s">
         <v>82</v>
       </c>
       <c r="C75" s="26" t="s">
@@ -2532,17 +2532,17 @@
         <v>2</v>
       </c>
       <c r="E75" s="13"/>
-      <c r="F75" s="39" t="s">
+      <c r="F75" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G75" s="42">
+      <c r="G75" s="47">
         <v>6</v>
       </c>
       <c r="H75" s="35"/>
     </row>
     <row r="76" spans="1:10" ht="36" x14ac:dyDescent="0.5">
-      <c r="A76" s="45"/>
-      <c r="B76" s="49"/>
+      <c r="A76" s="39"/>
+      <c r="B76" s="42"/>
       <c r="C76" s="26" t="s">
         <v>84</v>
       </c>
@@ -2552,13 +2552,13 @@
       <c r="E76" s="29">
         <v>6</v>
       </c>
-      <c r="F76" s="40"/>
-      <c r="G76" s="47"/>
+      <c r="F76" s="45"/>
+      <c r="G76" s="48"/>
       <c r="H76" s="35"/>
     </row>
     <row r="77" spans="1:10" ht="36" x14ac:dyDescent="0.5">
-      <c r="A77" s="46"/>
-      <c r="B77" s="50"/>
+      <c r="A77" s="40"/>
+      <c r="B77" s="43"/>
       <c r="C77" s="26" t="s">
         <v>85</v>
       </c>
@@ -2566,15 +2566,15 @@
         <v>2</v>
       </c>
       <c r="E77" s="14"/>
-      <c r="F77" s="41"/>
-      <c r="G77" s="43"/>
+      <c r="F77" s="46"/>
+      <c r="G77" s="49"/>
       <c r="H77" s="35"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A78" s="44">
+      <c r="A78" s="38">
         <v>46111</v>
       </c>
-      <c r="B78" s="48" t="s">
+      <c r="B78" s="41" t="s">
         <v>86</v>
       </c>
       <c r="C78" s="28" t="s">
@@ -2584,17 +2584,17 @@
         <v>2</v>
       </c>
       <c r="E78" s="13"/>
-      <c r="F78" s="39" t="s">
+      <c r="F78" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G78" s="42">
+      <c r="G78" s="47">
         <v>6</v>
       </c>
       <c r="H78" s="35"/>
     </row>
     <row r="79" spans="1:10" ht="36" x14ac:dyDescent="0.5">
-      <c r="A79" s="45"/>
-      <c r="B79" s="49"/>
+      <c r="A79" s="39"/>
+      <c r="B79" s="42"/>
       <c r="C79" s="28" t="s">
         <v>88</v>
       </c>
@@ -2604,13 +2604,13 @@
       <c r="E79" s="29">
         <v>6</v>
       </c>
-      <c r="F79" s="40"/>
-      <c r="G79" s="47"/>
+      <c r="F79" s="45"/>
+      <c r="G79" s="48"/>
       <c r="H79" s="35"/>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A80" s="46"/>
-      <c r="B80" s="50"/>
+      <c r="A80" s="40"/>
+      <c r="B80" s="43"/>
       <c r="C80" s="28" t="s">
         <v>89</v>
       </c>
@@ -2618,15 +2618,15 @@
         <v>2</v>
       </c>
       <c r="E80" s="14"/>
-      <c r="F80" s="41"/>
-      <c r="G80" s="43"/>
+      <c r="F80" s="46"/>
+      <c r="G80" s="49"/>
       <c r="H80" s="35"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A81" s="44">
+      <c r="A81" s="38">
         <v>46112</v>
       </c>
-      <c r="B81" s="48" t="s">
+      <c r="B81" s="41" t="s">
         <v>90</v>
       </c>
       <c r="C81" s="28" t="s">
@@ -2636,17 +2636,17 @@
         <v>2</v>
       </c>
       <c r="E81" s="13"/>
-      <c r="F81" s="39" t="s">
+      <c r="F81" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G81" s="42">
+      <c r="G81" s="47">
         <v>6</v>
       </c>
       <c r="H81" s="35"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A82" s="45"/>
-      <c r="B82" s="49"/>
+      <c r="A82" s="39"/>
+      <c r="B82" s="42"/>
       <c r="C82" s="28" t="s">
         <v>92</v>
       </c>
@@ -2656,13 +2656,13 @@
       <c r="E82" s="29">
         <v>6</v>
       </c>
-      <c r="F82" s="40"/>
-      <c r="G82" s="47"/>
+      <c r="F82" s="45"/>
+      <c r="G82" s="48"/>
       <c r="H82" s="35"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A83" s="46"/>
-      <c r="B83" s="50"/>
+      <c r="A83" s="40"/>
+      <c r="B83" s="43"/>
       <c r="C83" s="28" t="s">
         <v>93</v>
       </c>
@@ -2670,15 +2670,15 @@
         <v>2</v>
       </c>
       <c r="E83" s="14"/>
-      <c r="F83" s="41"/>
-      <c r="G83" s="43"/>
+      <c r="F83" s="46"/>
+      <c r="G83" s="49"/>
       <c r="H83" s="35"/>
     </row>
     <row r="84" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A84" s="44">
+      <c r="A84" s="38">
         <v>46113</v>
       </c>
-      <c r="B84" s="48" t="s">
+      <c r="B84" s="41" t="s">
         <v>94</v>
       </c>
       <c r="C84" s="28" t="s">
@@ -2688,17 +2688,17 @@
         <v>2</v>
       </c>
       <c r="E84" s="13"/>
-      <c r="F84" s="39" t="s">
+      <c r="F84" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G84" s="42">
+      <c r="G84" s="47">
         <v>6</v>
       </c>
       <c r="H84" s="35"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A85" s="45"/>
-      <c r="B85" s="49"/>
+      <c r="A85" s="39"/>
+      <c r="B85" s="42"/>
       <c r="C85" s="28" t="s">
         <v>96</v>
       </c>
@@ -2708,13 +2708,13 @@
       <c r="E85" s="29">
         <v>6</v>
       </c>
-      <c r="F85" s="40"/>
-      <c r="G85" s="47"/>
+      <c r="F85" s="45"/>
+      <c r="G85" s="48"/>
       <c r="H85" s="35"/>
     </row>
     <row r="86" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A86" s="46"/>
-      <c r="B86" s="50"/>
+      <c r="A86" s="40"/>
+      <c r="B86" s="43"/>
       <c r="C86" s="4" t="s">
         <v>97</v>
       </c>
@@ -2722,15 +2722,15 @@
         <v>2</v>
       </c>
       <c r="E86" s="14"/>
-      <c r="F86" s="41"/>
-      <c r="G86" s="43"/>
+      <c r="F86" s="46"/>
+      <c r="G86" s="49"/>
       <c r="H86" s="35"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A87" s="44">
+      <c r="A87" s="38">
         <v>46114</v>
       </c>
-      <c r="B87" s="48" t="s">
+      <c r="B87" s="41" t="s">
         <v>98</v>
       </c>
       <c r="C87" s="28" t="s">
@@ -2740,17 +2740,17 @@
         <v>2</v>
       </c>
       <c r="E87" s="13"/>
-      <c r="F87" s="39" t="s">
+      <c r="F87" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G87" s="42">
+      <c r="G87" s="47">
         <v>6</v>
       </c>
       <c r="H87" s="35"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A88" s="45"/>
-      <c r="B88" s="49"/>
+      <c r="A88" s="39"/>
+      <c r="B88" s="42"/>
       <c r="C88" s="28" t="s">
         <v>101</v>
       </c>
@@ -2760,13 +2760,13 @@
       <c r="E88" s="29">
         <v>6</v>
       </c>
-      <c r="F88" s="40"/>
-      <c r="G88" s="47"/>
+      <c r="F88" s="45"/>
+      <c r="G88" s="48"/>
       <c r="H88" s="35"/>
     </row>
     <row r="89" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A89" s="46"/>
-      <c r="B89" s="50"/>
+      <c r="A89" s="40"/>
+      <c r="B89" s="43"/>
       <c r="C89" s="28" t="s">
         <v>100</v>
       </c>
@@ -2774,15 +2774,15 @@
         <v>2</v>
       </c>
       <c r="E89" s="14"/>
-      <c r="F89" s="41"/>
-      <c r="G89" s="43"/>
+      <c r="F89" s="46"/>
+      <c r="G89" s="49"/>
       <c r="H89" s="35"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A90" s="44">
+      <c r="A90" s="38">
         <v>46115</v>
       </c>
-      <c r="B90" s="48" t="s">
+      <c r="B90" s="41" t="s">
         <v>102</v>
       </c>
       <c r="C90" s="28" t="s">
@@ -2794,17 +2794,17 @@
       <c r="E90" s="29">
         <v>6</v>
       </c>
-      <c r="F90" s="39" t="s">
+      <c r="F90" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G90" s="42">
+      <c r="G90" s="47">
         <v>6</v>
       </c>
       <c r="H90" s="35"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A91" s="46"/>
-      <c r="B91" s="50"/>
+      <c r="A91" s="40"/>
+      <c r="B91" s="43"/>
       <c r="C91" s="28" t="s">
         <v>104</v>
       </c>
@@ -2812,15 +2812,15 @@
         <v>3</v>
       </c>
       <c r="E91" s="14"/>
-      <c r="F91" s="41"/>
-      <c r="G91" s="43"/>
+      <c r="F91" s="46"/>
+      <c r="G91" s="49"/>
       <c r="H91" s="35"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A92" s="44">
+      <c r="A92" s="38">
         <v>46118</v>
       </c>
-      <c r="B92" s="48" t="s">
+      <c r="B92" s="41" t="s">
         <v>107</v>
       </c>
       <c r="C92" s="31" t="s">
@@ -2830,17 +2830,17 @@
         <v>2</v>
       </c>
       <c r="E92" s="13"/>
-      <c r="F92" s="39" t="s">
+      <c r="F92" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G92" s="42">
+      <c r="G92" s="47">
         <v>6</v>
       </c>
       <c r="H92" s="35"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A93" s="45"/>
-      <c r="B93" s="49"/>
+      <c r="A93" s="39"/>
+      <c r="B93" s="42"/>
       <c r="C93" s="31" t="s">
         <v>109</v>
       </c>
@@ -2850,13 +2850,13 @@
       <c r="E93" s="29">
         <v>6</v>
       </c>
-      <c r="F93" s="40"/>
-      <c r="G93" s="47"/>
+      <c r="F93" s="45"/>
+      <c r="G93" s="48"/>
       <c r="H93" s="35"/>
     </row>
     <row r="94" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A94" s="46"/>
-      <c r="B94" s="50"/>
+      <c r="A94" s="40"/>
+      <c r="B94" s="43"/>
       <c r="C94" s="31" t="s">
         <v>110</v>
       </c>
@@ -2864,15 +2864,15 @@
         <v>2</v>
       </c>
       <c r="E94" s="14"/>
-      <c r="F94" s="41"/>
-      <c r="G94" s="43"/>
+      <c r="F94" s="46"/>
+      <c r="G94" s="49"/>
       <c r="H94" s="35"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A95" s="44">
+      <c r="A95" s="38">
         <v>46119</v>
       </c>
-      <c r="B95" s="48" t="s">
+      <c r="B95" s="41" t="s">
         <v>111</v>
       </c>
       <c r="C95" s="32" t="s">
@@ -2882,17 +2882,17 @@
         <v>2</v>
       </c>
       <c r="E95" s="13"/>
-      <c r="F95" s="39" t="s">
+      <c r="F95" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G95" s="42">
+      <c r="G95" s="47">
         <v>6</v>
       </c>
       <c r="H95" s="35"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A96" s="45"/>
-      <c r="B96" s="49"/>
+      <c r="A96" s="39"/>
+      <c r="B96" s="42"/>
       <c r="C96" s="32" t="s">
         <v>113</v>
       </c>
@@ -2902,13 +2902,13 @@
       <c r="E96" s="29">
         <v>6</v>
       </c>
-      <c r="F96" s="40"/>
-      <c r="G96" s="47"/>
+      <c r="F96" s="45"/>
+      <c r="G96" s="48"/>
       <c r="H96" s="35"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A97" s="46"/>
-      <c r="B97" s="50"/>
+      <c r="A97" s="40"/>
+      <c r="B97" s="43"/>
       <c r="C97" s="32" t="s">
         <v>114</v>
       </c>
@@ -2916,15 +2916,15 @@
         <v>2</v>
       </c>
       <c r="E97" s="14"/>
-      <c r="F97" s="41"/>
-      <c r="G97" s="43"/>
+      <c r="F97" s="46"/>
+      <c r="G97" s="49"/>
       <c r="H97" s="35"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A98" s="44">
+      <c r="A98" s="38">
         <v>46120</v>
       </c>
-      <c r="B98" s="48" t="s">
+      <c r="B98" s="41" t="s">
         <v>115</v>
       </c>
       <c r="C98" s="32" t="s">
@@ -2934,17 +2934,17 @@
         <v>2</v>
       </c>
       <c r="E98" s="13"/>
-      <c r="F98" s="39" t="s">
+      <c r="F98" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G98" s="42">
+      <c r="G98" s="47">
         <v>6</v>
       </c>
       <c r="H98" s="35"/>
     </row>
     <row r="99" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A99" s="45"/>
-      <c r="B99" s="49"/>
+      <c r="A99" s="39"/>
+      <c r="B99" s="42"/>
       <c r="C99" s="32" t="s">
         <v>117</v>
       </c>
@@ -2954,13 +2954,13 @@
       <c r="E99" s="29">
         <v>6</v>
       </c>
-      <c r="F99" s="40"/>
-      <c r="G99" s="47"/>
+      <c r="F99" s="45"/>
+      <c r="G99" s="48"/>
       <c r="H99" s="35"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A100" s="46"/>
-      <c r="B100" s="50"/>
+      <c r="A100" s="40"/>
+      <c r="B100" s="43"/>
       <c r="C100" s="32" t="s">
         <v>118</v>
       </c>
@@ -2968,15 +2968,15 @@
         <v>2</v>
       </c>
       <c r="E100" s="14"/>
-      <c r="F100" s="41"/>
-      <c r="G100" s="43"/>
+      <c r="F100" s="46"/>
+      <c r="G100" s="49"/>
       <c r="H100" s="35"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A101" s="44">
+      <c r="A101" s="38">
         <v>46121</v>
       </c>
-      <c r="B101" s="48" t="s">
+      <c r="B101" s="41" t="s">
         <v>119</v>
       </c>
       <c r="C101" s="32" t="s">
@@ -2988,17 +2988,17 @@
       <c r="E101" s="29">
         <v>6</v>
       </c>
-      <c r="F101" s="39" t="s">
+      <c r="F101" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G101" s="42">
+      <c r="G101" s="47">
         <v>6</v>
       </c>
       <c r="H101" s="35"/>
     </row>
     <row r="102" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A102" s="46"/>
-      <c r="B102" s="50"/>
+      <c r="A102" s="40"/>
+      <c r="B102" s="43"/>
       <c r="C102" s="32" t="s">
         <v>121</v>
       </c>
@@ -3006,15 +3006,15 @@
         <v>4</v>
       </c>
       <c r="E102" s="14"/>
-      <c r="F102" s="41"/>
-      <c r="G102" s="43"/>
+      <c r="F102" s="46"/>
+      <c r="G102" s="49"/>
       <c r="H102" s="35"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A103" s="44">
+      <c r="A103" s="38">
         <v>46122</v>
       </c>
-      <c r="B103" s="48" t="s">
+      <c r="B103" s="41" t="s">
         <v>122</v>
       </c>
       <c r="C103" s="32" t="s">
@@ -3024,17 +3024,17 @@
         <v>2</v>
       </c>
       <c r="E103" s="13"/>
-      <c r="F103" s="39" t="s">
+      <c r="F103" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G103" s="42">
+      <c r="G103" s="47">
         <v>6</v>
       </c>
       <c r="H103" s="35"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A104" s="45"/>
-      <c r="B104" s="49"/>
+      <c r="A104" s="39"/>
+      <c r="B104" s="42"/>
       <c r="C104" s="32" t="s">
         <v>125</v>
       </c>
@@ -3044,13 +3044,13 @@
       <c r="E104" s="29">
         <v>6</v>
       </c>
-      <c r="F104" s="40"/>
-      <c r="G104" s="47"/>
+      <c r="F104" s="45"/>
+      <c r="G104" s="48"/>
       <c r="H104" s="35"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A105" s="46"/>
-      <c r="B105" s="50"/>
+      <c r="A105" s="40"/>
+      <c r="B105" s="43"/>
       <c r="C105" s="32" t="s">
         <v>124</v>
       </c>
@@ -3058,15 +3058,15 @@
         <v>3</v>
       </c>
       <c r="E105" s="14"/>
-      <c r="F105" s="41"/>
-      <c r="G105" s="43"/>
+      <c r="F105" s="46"/>
+      <c r="G105" s="49"/>
       <c r="H105" s="35"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A106" s="44">
+      <c r="A106" s="38">
         <v>46125</v>
       </c>
-      <c r="B106" s="48" t="s">
+      <c r="B106" s="41" t="s">
         <v>126</v>
       </c>
       <c r="C106" s="32" t="s">
@@ -3076,17 +3076,17 @@
         <v>2</v>
       </c>
       <c r="E106" s="13"/>
-      <c r="F106" s="39" t="s">
+      <c r="F106" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G106" s="42">
+      <c r="G106" s="47">
         <v>6</v>
       </c>
       <c r="H106" s="35"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A107" s="45"/>
-      <c r="B107" s="49"/>
+      <c r="A107" s="39"/>
+      <c r="B107" s="42"/>
       <c r="C107" s="32" t="s">
         <v>129</v>
       </c>
@@ -3096,13 +3096,13 @@
       <c r="E107" s="29">
         <v>6</v>
       </c>
-      <c r="F107" s="40"/>
-      <c r="G107" s="47"/>
+      <c r="F107" s="45"/>
+      <c r="G107" s="48"/>
       <c r="H107" s="35"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A108" s="46"/>
-      <c r="B108" s="50"/>
+      <c r="A108" s="40"/>
+      <c r="B108" s="43"/>
       <c r="C108" s="32" t="s">
         <v>128</v>
       </c>
@@ -3110,15 +3110,15 @@
         <v>3</v>
       </c>
       <c r="E108" s="14"/>
-      <c r="F108" s="41"/>
-      <c r="G108" s="43"/>
+      <c r="F108" s="46"/>
+      <c r="G108" s="49"/>
       <c r="H108" s="35"/>
     </row>
     <row r="109" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A109" s="44">
+      <c r="A109" s="38">
         <v>46126</v>
       </c>
-      <c r="B109" s="48" t="s">
+      <c r="B109" s="41" t="s">
         <v>130</v>
       </c>
       <c r="C109" s="32" t="s">
@@ -3128,17 +3128,17 @@
         <v>2</v>
       </c>
       <c r="E109" s="13"/>
-      <c r="F109" s="39" t="s">
+      <c r="F109" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G109" s="42">
+      <c r="G109" s="47">
         <v>6</v>
       </c>
       <c r="H109" s="35"/>
     </row>
     <row r="110" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A110" s="45"/>
-      <c r="B110" s="49"/>
+      <c r="A110" s="39"/>
+      <c r="B110" s="42"/>
       <c r="C110" s="32" t="s">
         <v>132</v>
       </c>
@@ -3148,13 +3148,13 @@
       <c r="E110" s="29">
         <v>6</v>
       </c>
-      <c r="F110" s="40"/>
-      <c r="G110" s="47"/>
+      <c r="F110" s="45"/>
+      <c r="G110" s="48"/>
       <c r="H110" s="35"/>
     </row>
     <row r="111" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A111" s="46"/>
-      <c r="B111" s="50"/>
+      <c r="A111" s="40"/>
+      <c r="B111" s="43"/>
       <c r="C111" s="32" t="s">
         <v>133</v>
       </c>
@@ -3162,15 +3162,15 @@
         <v>2</v>
       </c>
       <c r="E111" s="14"/>
-      <c r="F111" s="41"/>
-      <c r="G111" s="43"/>
+      <c r="F111" s="46"/>
+      <c r="G111" s="49"/>
       <c r="H111" s="35"/>
     </row>
     <row r="112" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A112" s="44">
+      <c r="A112" s="38">
         <v>46127</v>
       </c>
-      <c r="B112" s="48" t="s">
+      <c r="B112" s="41" t="s">
         <v>134</v>
       </c>
       <c r="C112" s="32" t="s">
@@ -3180,17 +3180,17 @@
         <v>2</v>
       </c>
       <c r="E112" s="13"/>
-      <c r="F112" s="39" t="s">
+      <c r="F112" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G112" s="42">
+      <c r="G112" s="47">
         <v>6</v>
       </c>
       <c r="H112" s="35"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A113" s="45"/>
-      <c r="B113" s="49"/>
+      <c r="A113" s="39"/>
+      <c r="B113" s="42"/>
       <c r="C113" s="32" t="s">
         <v>137</v>
       </c>
@@ -3200,13 +3200,13 @@
       <c r="E113" s="29">
         <v>6</v>
       </c>
-      <c r="F113" s="40"/>
-      <c r="G113" s="47"/>
+      <c r="F113" s="45"/>
+      <c r="G113" s="48"/>
       <c r="H113" s="35"/>
     </row>
     <row r="114" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A114" s="46"/>
-      <c r="B114" s="50"/>
+      <c r="A114" s="40"/>
+      <c r="B114" s="43"/>
       <c r="C114" s="32" t="s">
         <v>136</v>
       </c>
@@ -3214,15 +3214,15 @@
         <v>2</v>
       </c>
       <c r="E114" s="14"/>
-      <c r="F114" s="41"/>
-      <c r="G114" s="43"/>
+      <c r="F114" s="46"/>
+      <c r="G114" s="49"/>
       <c r="H114" s="35"/>
     </row>
     <row r="115" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A115" s="44">
+      <c r="A115" s="38">
         <v>46128</v>
       </c>
-      <c r="B115" s="48" t="s">
+      <c r="B115" s="41" t="s">
         <v>138</v>
       </c>
       <c r="C115" s="32" t="s">
@@ -3232,17 +3232,17 @@
         <v>3</v>
       </c>
       <c r="E115" s="13"/>
-      <c r="F115" s="39" t="s">
+      <c r="F115" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G115" s="42">
+      <c r="G115" s="47">
         <v>6</v>
       </c>
       <c r="H115" s="35"/>
     </row>
     <row r="116" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A116" s="45"/>
-      <c r="B116" s="49"/>
+      <c r="A116" s="39"/>
+      <c r="B116" s="42"/>
       <c r="C116" s="32" t="s">
         <v>140</v>
       </c>
@@ -3252,13 +3252,13 @@
       <c r="E116" s="29">
         <v>6</v>
       </c>
-      <c r="F116" s="40"/>
-      <c r="G116" s="47"/>
+      <c r="F116" s="45"/>
+      <c r="G116" s="48"/>
       <c r="H116" s="35"/>
     </row>
     <row r="117" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A117" s="46"/>
-      <c r="B117" s="50"/>
+      <c r="A117" s="40"/>
+      <c r="B117" s="43"/>
       <c r="C117" s="32" t="s">
         <v>141</v>
       </c>
@@ -3266,15 +3266,15 @@
         <v>1</v>
       </c>
       <c r="E117" s="14"/>
-      <c r="F117" s="41"/>
-      <c r="G117" s="43"/>
+      <c r="F117" s="46"/>
+      <c r="G117" s="49"/>
       <c r="H117" s="35"/>
     </row>
     <row r="118" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A118" s="44">
+      <c r="A118" s="38">
         <v>46129</v>
       </c>
-      <c r="B118" s="48" t="s">
+      <c r="B118" s="41" t="s">
         <v>142</v>
       </c>
       <c r="C118" s="32" t="s">
@@ -3284,17 +3284,17 @@
         <v>2</v>
       </c>
       <c r="E118" s="13"/>
-      <c r="F118" s="39" t="s">
+      <c r="F118" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G118" s="42">
+      <c r="G118" s="47">
         <v>6</v>
       </c>
       <c r="H118" s="35"/>
     </row>
     <row r="119" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A119" s="45"/>
-      <c r="B119" s="49"/>
+      <c r="A119" s="39"/>
+      <c r="B119" s="42"/>
       <c r="C119" s="32" t="s">
         <v>144</v>
       </c>
@@ -3304,13 +3304,13 @@
       <c r="E119" s="29">
         <v>6</v>
       </c>
-      <c r="F119" s="40"/>
-      <c r="G119" s="47"/>
+      <c r="F119" s="45"/>
+      <c r="G119" s="48"/>
       <c r="H119" s="35"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A120" s="46"/>
-      <c r="B120" s="50"/>
+      <c r="A120" s="40"/>
+      <c r="B120" s="43"/>
       <c r="C120" s="4" t="s">
         <v>145</v>
       </c>
@@ -3318,15 +3318,15 @@
         <v>2</v>
       </c>
       <c r="E120" s="14"/>
-      <c r="F120" s="41"/>
-      <c r="G120" s="43"/>
+      <c r="F120" s="46"/>
+      <c r="G120" s="49"/>
       <c r="H120" s="35"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A121" s="44">
+      <c r="A121" s="38">
         <v>46132</v>
       </c>
-      <c r="B121" s="48" t="s">
+      <c r="B121" s="41" t="s">
         <v>146</v>
       </c>
       <c r="C121" s="32" t="s">
@@ -3336,17 +3336,17 @@
         <v>2</v>
       </c>
       <c r="E121" s="13"/>
-      <c r="F121" s="39" t="s">
+      <c r="F121" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G121" s="42">
+      <c r="G121" s="47">
         <v>6</v>
       </c>
       <c r="H121" s="35"/>
     </row>
     <row r="122" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A122" s="45"/>
-      <c r="B122" s="49"/>
+      <c r="A122" s="39"/>
+      <c r="B122" s="42"/>
       <c r="C122" s="32" t="s">
         <v>148</v>
       </c>
@@ -3356,13 +3356,13 @@
       <c r="E122" s="29">
         <v>6</v>
       </c>
-      <c r="F122" s="40"/>
-      <c r="G122" s="47"/>
+      <c r="F122" s="45"/>
+      <c r="G122" s="48"/>
       <c r="H122" s="35"/>
     </row>
     <row r="123" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A123" s="46"/>
-      <c r="B123" s="50"/>
+      <c r="A123" s="40"/>
+      <c r="B123" s="43"/>
       <c r="C123" s="32" t="s">
         <v>149</v>
       </c>
@@ -3370,15 +3370,15 @@
         <v>2</v>
       </c>
       <c r="E123" s="14"/>
-      <c r="F123" s="41"/>
-      <c r="G123" s="43"/>
+      <c r="F123" s="46"/>
+      <c r="G123" s="49"/>
       <c r="H123" s="35"/>
     </row>
     <row r="124" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A124" s="44">
+      <c r="A124" s="38">
         <v>46133</v>
       </c>
-      <c r="B124" s="48" t="s">
+      <c r="B124" s="41" t="s">
         <v>150</v>
       </c>
       <c r="C124" s="4" t="s">
@@ -3390,17 +3390,17 @@
       <c r="E124" s="29">
         <v>6</v>
       </c>
-      <c r="F124" s="39" t="s">
+      <c r="F124" s="44" t="s">
         <v>151</v>
       </c>
-      <c r="G124" s="42">
+      <c r="G124" s="47">
         <v>6</v>
       </c>
       <c r="H124" s="35"/>
     </row>
     <row r="125" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A125" s="46"/>
-      <c r="B125" s="50"/>
+      <c r="A125" s="40"/>
+      <c r="B125" s="43"/>
       <c r="C125" s="32" t="s">
         <v>175</v>
       </c>
@@ -3408,15 +3408,15 @@
         <v>3</v>
       </c>
       <c r="E125" s="14"/>
-      <c r="F125" s="41"/>
-      <c r="G125" s="43"/>
+      <c r="F125" s="46"/>
+      <c r="G125" s="49"/>
       <c r="H125" s="35"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A126" s="44">
+      <c r="A126" s="38">
         <v>46134</v>
       </c>
-      <c r="B126" s="48" t="s">
+      <c r="B126" s="41" t="s">
         <v>152</v>
       </c>
       <c r="C126" s="32" t="s">
@@ -3428,17 +3428,17 @@
       <c r="E126" s="29">
         <v>6</v>
       </c>
-      <c r="F126" s="39" t="s">
+      <c r="F126" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G126" s="42">
+      <c r="G126" s="47">
         <v>6</v>
       </c>
       <c r="H126" s="35"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A127" s="46"/>
-      <c r="B127" s="50"/>
+      <c r="A127" s="40"/>
+      <c r="B127" s="43"/>
       <c r="C127" s="32" t="s">
         <v>154</v>
       </c>
@@ -3446,15 +3446,15 @@
         <v>3</v>
       </c>
       <c r="E127" s="29"/>
-      <c r="F127" s="41"/>
-      <c r="G127" s="43"/>
+      <c r="F127" s="46"/>
+      <c r="G127" s="49"/>
       <c r="H127" s="35"/>
     </row>
     <row r="128" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A128" s="44">
+      <c r="A128" s="38">
         <v>46135</v>
       </c>
-      <c r="B128" s="48" t="s">
+      <c r="B128" s="41" t="s">
         <v>176</v>
       </c>
       <c r="C128" s="32" t="s">
@@ -3473,8 +3473,8 @@
       <c r="H128" s="35"/>
     </row>
     <row r="129" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A129" s="45"/>
-      <c r="B129" s="49"/>
+      <c r="A129" s="39"/>
+      <c r="B129" s="42"/>
       <c r="C129" s="32" t="s">
         <v>178</v>
       </c>
@@ -3489,8 +3489,8 @@
       <c r="H129" s="35"/>
     </row>
     <row r="130" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A130" s="46"/>
-      <c r="B130" s="50"/>
+      <c r="A130" s="40"/>
+      <c r="B130" s="43"/>
       <c r="C130" s="32" t="s">
         <v>179</v>
       </c>
@@ -3503,10 +3503,10 @@
       <c r="H130" s="35"/>
     </row>
     <row r="131" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A131" s="44">
+      <c r="A131" s="38">
         <v>46136</v>
       </c>
-      <c r="B131" s="48" t="s">
+      <c r="B131" s="41" t="s">
         <v>180</v>
       </c>
       <c r="C131" s="33" t="s">
@@ -3516,17 +3516,17 @@
         <v>2</v>
       </c>
       <c r="E131" s="13"/>
-      <c r="F131" s="39" t="s">
+      <c r="F131" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G131" s="42">
+      <c r="G131" s="47">
         <v>6</v>
       </c>
       <c r="H131" s="35"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A132" s="45"/>
-      <c r="B132" s="49"/>
+      <c r="A132" s="39"/>
+      <c r="B132" s="42"/>
       <c r="C132" s="33" t="s">
         <v>182</v>
       </c>
@@ -3536,13 +3536,13 @@
       <c r="E132" s="29">
         <v>6</v>
       </c>
-      <c r="F132" s="40"/>
-      <c r="G132" s="47"/>
+      <c r="F132" s="45"/>
+      <c r="G132" s="48"/>
       <c r="H132" s="35"/>
     </row>
     <row r="133" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A133" s="46"/>
-      <c r="B133" s="50"/>
+      <c r="A133" s="40"/>
+      <c r="B133" s="43"/>
       <c r="C133" s="33" t="s">
         <v>183</v>
       </c>
@@ -3550,15 +3550,15 @@
         <v>2</v>
       </c>
       <c r="E133" s="14"/>
-      <c r="F133" s="41"/>
-      <c r="G133" s="43"/>
+      <c r="F133" s="46"/>
+      <c r="G133" s="49"/>
       <c r="H133" s="35"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A134" s="44">
+      <c r="A134" s="38">
         <v>46139</v>
       </c>
-      <c r="B134" s="48" t="s">
+      <c r="B134" s="41" t="s">
         <v>184</v>
       </c>
       <c r="C134" s="33" t="s">
@@ -3568,17 +3568,17 @@
         <v>2</v>
       </c>
       <c r="E134" s="13"/>
-      <c r="F134" s="39" t="s">
+      <c r="F134" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G134" s="42">
+      <c r="G134" s="47">
         <v>6</v>
       </c>
       <c r="H134" s="35"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A135" s="45"/>
-      <c r="B135" s="49"/>
+      <c r="A135" s="39"/>
+      <c r="B135" s="42"/>
       <c r="C135" s="33" t="s">
         <v>186</v>
       </c>
@@ -3588,13 +3588,13 @@
       <c r="E135" s="29">
         <v>6</v>
       </c>
-      <c r="F135" s="40"/>
-      <c r="G135" s="47"/>
+      <c r="F135" s="45"/>
+      <c r="G135" s="48"/>
       <c r="H135" s="35"/>
     </row>
     <row r="136" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A136" s="46"/>
-      <c r="B136" s="50"/>
+      <c r="A136" s="40"/>
+      <c r="B136" s="43"/>
       <c r="C136" s="33" t="s">
         <v>187</v>
       </c>
@@ -3602,15 +3602,15 @@
         <v>2</v>
       </c>
       <c r="E136" s="14"/>
-      <c r="F136" s="41"/>
-      <c r="G136" s="43"/>
+      <c r="F136" s="46"/>
+      <c r="G136" s="49"/>
       <c r="H136" s="35"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A137" s="44">
+      <c r="A137" s="38">
         <v>46140</v>
       </c>
-      <c r="B137" s="48" t="s">
+      <c r="B137" s="41" t="s">
         <v>188</v>
       </c>
       <c r="C137" s="33" t="s">
@@ -3622,17 +3622,17 @@
       <c r="E137" s="29">
         <v>6</v>
       </c>
-      <c r="F137" s="39" t="s">
+      <c r="F137" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G137" s="42">
+      <c r="G137" s="47">
         <v>6</v>
       </c>
       <c r="H137" s="35"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A138" s="46"/>
-      <c r="B138" s="50"/>
+      <c r="A138" s="40"/>
+      <c r="B138" s="43"/>
       <c r="C138" s="33" t="s">
         <v>186</v>
       </c>
@@ -3640,15 +3640,15 @@
         <v>3</v>
       </c>
       <c r="E138" s="14"/>
-      <c r="F138" s="41"/>
-      <c r="G138" s="43"/>
+      <c r="F138" s="46"/>
+      <c r="G138" s="49"/>
       <c r="H138" s="35"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A139" s="44">
+      <c r="A139" s="38">
         <v>46141</v>
       </c>
-      <c r="B139" s="48" t="s">
+      <c r="B139" s="41" t="s">
         <v>193</v>
       </c>
       <c r="C139" s="33" t="s">
@@ -3658,17 +3658,17 @@
         <v>2</v>
       </c>
       <c r="E139" s="13"/>
-      <c r="F139" s="39" t="s">
+      <c r="F139" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G139" s="42">
+      <c r="G139" s="47">
         <v>6</v>
       </c>
       <c r="H139" s="35"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A140" s="45"/>
-      <c r="B140" s="49"/>
+      <c r="A140" s="39"/>
+      <c r="B140" s="42"/>
       <c r="C140" s="33" t="s">
         <v>191</v>
       </c>
@@ -3678,13 +3678,13 @@
       <c r="E140" s="29">
         <v>6</v>
       </c>
-      <c r="F140" s="40"/>
-      <c r="G140" s="47"/>
+      <c r="F140" s="45"/>
+      <c r="G140" s="48"/>
       <c r="H140" s="35"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A141" s="46"/>
-      <c r="B141" s="50"/>
+      <c r="A141" s="40"/>
+      <c r="B141" s="43"/>
       <c r="C141" s="33" t="s">
         <v>192</v>
       </c>
@@ -3692,36 +3692,36 @@
         <v>2</v>
       </c>
       <c r="E141" s="14"/>
-      <c r="F141" s="41"/>
-      <c r="G141" s="43"/>
+      <c r="F141" s="46"/>
+      <c r="G141" s="49"/>
       <c r="H141" s="35"/>
     </row>
     <row r="142" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A142" s="44">
+      <c r="A142" s="38">
         <v>46142</v>
       </c>
-      <c r="B142" s="48" t="s">
+      <c r="B142" s="41" t="s">
         <v>194</v>
       </c>
-      <c r="C142" s="38" t="s">
+      <c r="C142" s="37" t="s">
         <v>195</v>
       </c>
       <c r="D142" s="15">
         <v>2</v>
       </c>
       <c r="E142" s="13"/>
-      <c r="F142" s="39" t="s">
+      <c r="F142" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G142" s="42">
+      <c r="G142" s="47">
         <v>6</v>
       </c>
       <c r="H142" s="35"/>
     </row>
     <row r="143" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A143" s="45"/>
-      <c r="B143" s="49"/>
-      <c r="C143" s="38" t="s">
+      <c r="A143" s="39"/>
+      <c r="B143" s="42"/>
+      <c r="C143" s="37" t="s">
         <v>196</v>
       </c>
       <c r="D143" s="15">
@@ -3730,22 +3730,22 @@
       <c r="E143" s="29">
         <v>6</v>
       </c>
-      <c r="F143" s="40"/>
-      <c r="G143" s="47"/>
+      <c r="F143" s="45"/>
+      <c r="G143" s="48"/>
       <c r="H143" s="35"/>
     </row>
     <row r="144" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A144" s="46"/>
-      <c r="B144" s="50"/>
-      <c r="C144" s="38" t="s">
+      <c r="A144" s="40"/>
+      <c r="B144" s="43"/>
+      <c r="C144" s="37" t="s">
         <v>197</v>
       </c>
       <c r="D144" s="15">
         <v>2</v>
       </c>
-      <c r="E144" s="38"/>
-      <c r="F144" s="41"/>
-      <c r="G144" s="43"/>
+      <c r="E144" s="37"/>
+      <c r="F144" s="46"/>
+      <c r="G144" s="49"/>
       <c r="H144" s="35"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.5">
@@ -3762,13 +3762,13 @@
         <v>9</v>
       </c>
       <c r="E147" s="21">
-        <f>SUM(E9:E142)</f>
-        <v>258</v>
+        <f>SUM(E10:E143)</f>
+        <v>264</v>
       </c>
       <c r="F147" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="G147" s="37">
+      <c r="G147" s="53">
         <f>SUM(G9:G142)</f>
         <v>264</v>
       </c>
@@ -3923,28 +3923,135 @@
     </row>
   </sheetData>
   <mergeCells count="177">
-    <mergeCell ref="A142:A144"/>
-    <mergeCell ref="B142:B144"/>
-    <mergeCell ref="F142:F144"/>
-    <mergeCell ref="G142:G144"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="B139:B141"/>
-    <mergeCell ref="A139:A141"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="A137:A138"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="F109:F111"/>
-    <mergeCell ref="G109:G111"/>
-    <mergeCell ref="A112:A114"/>
-    <mergeCell ref="B112:B114"/>
-    <mergeCell ref="F112:F114"/>
-    <mergeCell ref="G112:G114"/>
-    <mergeCell ref="F57:F59"/>
-    <mergeCell ref="G57:G59"/>
-    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="F134:F136"/>
+    <mergeCell ref="F90:F91"/>
+    <mergeCell ref="G90:G91"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="F92:F94"/>
+    <mergeCell ref="G92:G94"/>
+    <mergeCell ref="A87:A89"/>
+    <mergeCell ref="B87:B89"/>
+    <mergeCell ref="F87:F89"/>
+    <mergeCell ref="G87:G89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="F121:F123"/>
+    <mergeCell ref="G121:G123"/>
+    <mergeCell ref="F128:F130"/>
+    <mergeCell ref="G128:G130"/>
+    <mergeCell ref="A106:A108"/>
+    <mergeCell ref="B106:B108"/>
+    <mergeCell ref="F106:F108"/>
+    <mergeCell ref="G106:G108"/>
+    <mergeCell ref="A109:A111"/>
+    <mergeCell ref="B109:B111"/>
+    <mergeCell ref="G84:G86"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="B131:B133"/>
+    <mergeCell ref="F131:F133"/>
+    <mergeCell ref="G131:G133"/>
+    <mergeCell ref="F98:F100"/>
+    <mergeCell ref="G98:G100"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B101:B102"/>
+    <mergeCell ref="F101:F102"/>
+    <mergeCell ref="G101:G102"/>
+    <mergeCell ref="A103:A105"/>
+    <mergeCell ref="B103:B105"/>
+    <mergeCell ref="F103:F105"/>
+    <mergeCell ref="G103:G105"/>
+    <mergeCell ref="F126:F127"/>
+    <mergeCell ref="G126:G127"/>
+    <mergeCell ref="A121:A123"/>
+    <mergeCell ref="B121:B123"/>
+    <mergeCell ref="F33:F36"/>
+    <mergeCell ref="G33:G36"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="A75:A77"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="F75:F77"/>
+    <mergeCell ref="G75:G77"/>
+    <mergeCell ref="A78:A80"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="F78:F80"/>
+    <mergeCell ref="G78:G80"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="F37:F40"/>
+    <mergeCell ref="G37:G40"/>
+    <mergeCell ref="A41:A44"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="F41:F44"/>
+    <mergeCell ref="G41:G44"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="F45:F47"/>
+    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="F48:F50"/>
+    <mergeCell ref="G22:G25"/>
+    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="G26:G29"/>
+    <mergeCell ref="F22:F25"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="G12:G15"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="G48:G50"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="F51:F53"/>
+    <mergeCell ref="G51:G53"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="F54:F56"/>
+    <mergeCell ref="G54:G56"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="G60:G63"/>
+    <mergeCell ref="G95:G97"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="F95:F97"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="B68:B71"/>
+    <mergeCell ref="F68:F71"/>
+    <mergeCell ref="G68:G71"/>
+    <mergeCell ref="A64:A67"/>
+    <mergeCell ref="B64:B67"/>
+    <mergeCell ref="F64:F67"/>
+    <mergeCell ref="G64:G67"/>
+    <mergeCell ref="A72:A74"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="F72:F74"/>
+    <mergeCell ref="G72:G74"/>
+    <mergeCell ref="A81:A83"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="F81:F83"/>
+    <mergeCell ref="G81:G83"/>
+    <mergeCell ref="A84:A86"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="F84:F86"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A37:A40"/>
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="B33:B36"/>
@@ -3969,137 +4076,30 @@
     <mergeCell ref="G124:G125"/>
     <mergeCell ref="A134:A136"/>
     <mergeCell ref="B134:B136"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="A33:A36"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A142:A144"/>
+    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="F142:F144"/>
+    <mergeCell ref="G142:G144"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="B139:B141"/>
+    <mergeCell ref="A139:A141"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="A137:A138"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="F109:F111"/>
+    <mergeCell ref="G109:G111"/>
+    <mergeCell ref="A112:A114"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="F112:F114"/>
+    <mergeCell ref="G112:G114"/>
+    <mergeCell ref="F57:F59"/>
+    <mergeCell ref="G57:G59"/>
+    <mergeCell ref="A60:A63"/>
     <mergeCell ref="B60:B63"/>
     <mergeCell ref="F60:F63"/>
-    <mergeCell ref="G60:G63"/>
-    <mergeCell ref="G95:G97"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="F95:F97"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="B68:B71"/>
-    <mergeCell ref="F68:F71"/>
-    <mergeCell ref="G68:G71"/>
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="B64:B67"/>
-    <mergeCell ref="F64:F67"/>
-    <mergeCell ref="G64:G67"/>
-    <mergeCell ref="A72:A74"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="F72:F74"/>
-    <mergeCell ref="G72:G74"/>
-    <mergeCell ref="A81:A83"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="F81:F83"/>
-    <mergeCell ref="G81:G83"/>
-    <mergeCell ref="A84:A86"/>
-    <mergeCell ref="G48:G50"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="F51:F53"/>
-    <mergeCell ref="G51:G53"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="B54:B56"/>
-    <mergeCell ref="F54:F56"/>
-    <mergeCell ref="G54:G56"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="G22:G25"/>
-    <mergeCell ref="F26:F29"/>
-    <mergeCell ref="G26:G29"/>
-    <mergeCell ref="F22:F25"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="F19:F21"/>
-    <mergeCell ref="G19:G21"/>
-    <mergeCell ref="G12:G15"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="F33:F36"/>
-    <mergeCell ref="G33:G36"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="A75:A77"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="F75:F77"/>
-    <mergeCell ref="G75:G77"/>
-    <mergeCell ref="A78:A80"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="F78:F80"/>
-    <mergeCell ref="G78:G80"/>
-    <mergeCell ref="F30:F32"/>
-    <mergeCell ref="G30:G32"/>
-    <mergeCell ref="F37:F40"/>
-    <mergeCell ref="G37:G40"/>
-    <mergeCell ref="A41:A44"/>
-    <mergeCell ref="B41:B44"/>
-    <mergeCell ref="F41:F44"/>
-    <mergeCell ref="G41:G44"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="F45:F47"/>
-    <mergeCell ref="G45:G47"/>
-    <mergeCell ref="F48:F50"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="F84:F86"/>
-    <mergeCell ref="G84:G86"/>
-    <mergeCell ref="A131:A133"/>
-    <mergeCell ref="B131:B133"/>
-    <mergeCell ref="F131:F133"/>
-    <mergeCell ref="G131:G133"/>
-    <mergeCell ref="F98:F100"/>
-    <mergeCell ref="G98:G100"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B101:B102"/>
-    <mergeCell ref="F101:F102"/>
-    <mergeCell ref="G101:G102"/>
-    <mergeCell ref="A103:A105"/>
-    <mergeCell ref="B103:B105"/>
-    <mergeCell ref="F103:F105"/>
-    <mergeCell ref="G103:G105"/>
-    <mergeCell ref="F126:F127"/>
-    <mergeCell ref="G126:G127"/>
-    <mergeCell ref="A121:A123"/>
-    <mergeCell ref="B121:B123"/>
-    <mergeCell ref="F134:F136"/>
-    <mergeCell ref="F90:F91"/>
-    <mergeCell ref="G90:G91"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="F92:F94"/>
-    <mergeCell ref="G92:G94"/>
-    <mergeCell ref="A87:A89"/>
-    <mergeCell ref="B87:B89"/>
-    <mergeCell ref="F87:F89"/>
-    <mergeCell ref="G87:G89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="F121:F123"/>
-    <mergeCell ref="G121:G123"/>
-    <mergeCell ref="F128:F130"/>
-    <mergeCell ref="G128:G130"/>
-    <mergeCell ref="A106:A108"/>
-    <mergeCell ref="B106:B108"/>
-    <mergeCell ref="F106:F108"/>
-    <mergeCell ref="G106:G108"/>
-    <mergeCell ref="A109:A111"/>
-    <mergeCell ref="B109:B111"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
